--- a/matrix_bot/m_registrations.xlsx
+++ b/matrix_bot/m_registrations.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Junsu Choi\Desktop\jikbak\Discord bot project\matrix_bot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D03823BB-58CC-4D46-ADFB-F31652C15E17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E15109D-13B6-485D-B9E5-D46933AC5674}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5310" yWindow="2220" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="출석체크" sheetId="1" r:id="rId1"/>
@@ -79,9 +79,6 @@
     <t>김윤호</t>
   </si>
   <si>
-    <t>김지윤</t>
-  </si>
-  <si>
     <t>박선후</t>
   </si>
   <si>
@@ -128,6 +125,9 @@
   </si>
   <si>
     <t>이승아</t>
+  </si>
+  <si>
+    <t>이승재</t>
   </si>
   <si>
     <t>이유찬</t>
@@ -188,10 +188,8 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -202,7 +200,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -220,19 +218,6 @@
       <top style="medium">
         <color rgb="FFCCCCCC"/>
       </top>
-      <bottom style="medium">
-        <color rgb="FFCCCCCC"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFCCCCCC"/>
-      </right>
-      <top/>
       <bottom style="medium">
         <color rgb="FFCCCCCC"/>
       </bottom>
@@ -279,17 +264,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -573,227 +555,335 @@
   <dimension ref="A1:L37"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:12" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="4" t="s">
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="4" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="4" t="s">
         <v>13</v>
       </c>
+      <c r="E3" t="b">
+        <v>1</v>
+      </c>
+      <c r="H3" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="4" spans="1:12" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="4" t="s">
         <v>14</v>
       </c>
+      <c r="H4" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" spans="1:12" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="4" t="s">
         <v>15</v>
       </c>
+      <c r="E5" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="6" spans="1:12" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="4" t="s">
         <v>16</v>
       </c>
+      <c r="E6" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="7" spans="1:12" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="4" t="s">
         <v>17</v>
       </c>
+      <c r="H7" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="8" spans="1:12" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="4" t="s">
         <v>18</v>
       </c>
+      <c r="E8" t="b">
+        <v>1</v>
+      </c>
+      <c r="H8" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="1:12" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="4" t="s">
         <v>19</v>
       </c>
+      <c r="E9" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="10" spans="1:12" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="4" t="s">
         <v>20</v>
       </c>
+      <c r="E10" t="b">
+        <v>1</v>
+      </c>
+      <c r="H10" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="11" spans="1:12" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="4" t="s">
         <v>21</v>
       </c>
+      <c r="E11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H11" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="12" spans="1:12" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="4" t="s">
         <v>22</v>
       </c>
+      <c r="E12" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="13" spans="1:12" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="4" t="s">
         <v>23</v>
       </c>
+      <c r="E13" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="14" spans="1:12" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="4" t="s">
         <v>24</v>
       </c>
+      <c r="E14" t="b">
+        <v>1</v>
+      </c>
+      <c r="H14" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="15" spans="1:12" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="4" t="s">
         <v>25</v>
       </c>
+      <c r="E15" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="16" spans="1:12" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="17" spans="1:1" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="1" t="s">
+    <row r="17" spans="1:8" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="18" spans="1:1" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="1" t="s">
+    <row r="18" spans="1:8" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="4" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="1:1" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="1" t="s">
+    <row r="19" spans="1:8" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="4" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="20" spans="1:1" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="1" t="s">
+      <c r="E19" t="b">
+        <v>1</v>
+      </c>
+      <c r="H19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="4" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="21" spans="1:1" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="1" t="s">
+    <row r="21" spans="1:8" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="4" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="22" spans="1:1" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="1" t="s">
+      <c r="E21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="4" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="23" spans="1:1" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="1" t="s">
+      <c r="E22" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="4" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="24" spans="1:1" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="1" t="s">
+      <c r="E23" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="4" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="25" spans="1:1" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="1" t="s">
+      <c r="E24" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="4" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="26" spans="1:1" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="1" t="s">
+    <row r="26" spans="1:8" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="4" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="27" spans="1:1" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="1" t="s">
+    <row r="27" spans="1:8" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="4" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="28" spans="1:1" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="1" t="s">
+      <c r="E27" t="b">
+        <v>1</v>
+      </c>
+      <c r="H27" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="4" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="29" spans="1:1" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="1" t="s">
+      <c r="E28" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="4" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="30" spans="1:1" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="1" t="s">
+      <c r="H29" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="4" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="31" spans="1:1" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="1" t="s">
+      <c r="E30" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="4" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="32" spans="1:1" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="1" t="s">
+    <row r="32" spans="1:8" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="4" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="33" spans="1:1" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="1" t="s">
+      <c r="E32" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="4" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="34" spans="1:1" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="1" t="s">
+      <c r="H33" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="4" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="35" spans="1:1" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="1" t="s">
+      <c r="H34" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="4" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="36" spans="1:1" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="1" t="s">
+      <c r="H35" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="4" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="37" spans="1:1" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="1" t="s">
+      <c r="H36" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="4" t="s">
         <v>47</v>
+      </c>
+      <c r="E37" t="b">
+        <v>1</v>
+      </c>
+      <c r="H37" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>